--- a/web/public/forms/orig/o-gaseol-haeche.xlsx
+++ b/web/public/forms/orig/o-gaseol-haeche.xlsx
@@ -587,9 +587,9 @@
       <col>0</col>
       <colOff>295275</colOff>
       <row>64</row>
-      <rowOff>47625</rowOff>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="2428875" cy="2181225"/>
+    <ext cx="2428875" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -614,7 +614,7 @@
       <row>64</row>
       <rowOff>47625</rowOff>
     </from>
-    <ext cx="2266950" cy="2181225"/>
+    <ext cx="2266950" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -642,9 +642,9 @@
       <col>0</col>
       <colOff>295275</colOff>
       <row>64</row>
-      <rowOff>47625</rowOff>
+      <rowOff>38100</rowOff>
     </from>
-    <ext cx="2428875" cy="2181225"/>
+    <ext cx="2428875" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -669,7 +669,7 @@
       <row>64</row>
       <rowOff>47625</rowOff>
     </from>
-    <ext cx="2266950" cy="2181225"/>
+    <ext cx="2266950" cy="2190750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -999,7 +999,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="69" t="inlineStr">
@@ -2692,7 +2692,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -8061,7 +8061,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="69" t="inlineStr">
@@ -8149,7 +8149,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="69" t="inlineStr">
@@ -9512,7 +9512,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="N1" s="69" t="inlineStr">
@@ -10726,7 +10726,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="69" t="inlineStr">

--- a/web/public/forms/orig/o-gaseol-haeche.xlsx
+++ b/web/public/forms/orig/o-gaseol-haeche.xlsx
@@ -915,7 +915,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4422,7 +4422,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
